--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0002T0006Z000C1N39_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0002T0006Z000C1N39_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>70.91689955753455</v>
+        <v>11.52399617809936</v>
       </c>
       <c r="D2" t="n">
-        <v>66.19537091966255</v>
+        <v>10.75674777444516</v>
       </c>
       <c r="E2" t="n">
-        <v>20.19927481180841</v>
+        <v>3.282382156918867</v>
       </c>
       <c r="F2" t="n">
-        <v>19.18059818061351</v>
+        <v>3.116847204349696</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.18474260055113</v>
+        <v>3.280020672589558</v>
       </c>
       <c r="D3" t="n">
-        <v>18.33804213352071</v>
+        <v>2.979931846697116</v>
       </c>
       <c r="E3" t="n">
-        <v>20.19927481180841</v>
+        <v>3.282382156918867</v>
       </c>
       <c r="F3" t="n">
-        <v>19.18059818061351</v>
+        <v>3.116847204349696</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.20172685697588</v>
+        <v>4.745280614258581</v>
       </c>
       <c r="D4" t="n">
-        <v>28.95504191926133</v>
+        <v>4.705194311879966</v>
       </c>
       <c r="E4" t="n">
-        <v>20.19927481180841</v>
+        <v>3.282382156918867</v>
       </c>
       <c r="F4" t="n">
-        <v>19.18059818061351</v>
+        <v>3.116847204349696</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>55.02187733580934</v>
+        <v>8.941055067069017</v>
       </c>
       <c r="D5" t="n">
-        <v>54.4942509056349</v>
+        <v>8.855315772165671</v>
       </c>
       <c r="E5" t="n">
-        <v>20.19927481180841</v>
+        <v>3.282382156918867</v>
       </c>
       <c r="F5" t="n">
-        <v>19.18059818061351</v>
+        <v>3.116847204349696</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
